--- a/results/Int All Data -0.6/Rando_2_permute.xlsx
+++ b/results/Int All Data -0.6/Rando_2_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7403723705063847</v>
+        <v>0.7344955002757783</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7338617338425342</v>
+        <v>0.7348089798996027</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7338617338425342</v>
+        <v>0.7358173160838086</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7340394188408934</v>
+        <v>0.735538919647283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7449738534255852</v>
+        <v>0.7353329586472201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7459493754843575</v>
+        <v>0.7332812030915095</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7421548058730303</v>
+        <v>0.7300411572913685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7427817651206792</v>
+        <v>0.7306330333517186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7399604485062592</v>
+        <v>0.7303195537278941</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7348067108377376</v>
+        <v>0.7332087676550467</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7516644441496604</v>
+        <v>0.7318167854724187</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7440707668032758</v>
+        <v>0.7347716276504388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7458814781716249</v>
+        <v>0.7341095852154911</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7461247914208516</v>
+        <v>0.7346663780885423</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.744208830490606</v>
+        <v>0.7353635037107888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7443446251160712</v>
+        <v>0.7342850011519853</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7443446251160712</v>
+        <v>0.7288528670469382</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7441714782414421</v>
+        <v>0.7216428356989758</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7433362889318653</v>
+        <v>0.7185080394607313</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7424988305604234</v>
+        <v>0.7179161634003812</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.743996062304948</v>
+        <v>0.7179512465876801</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7450417507383178</v>
+        <v>0.7162785989066613</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7453552303621422</v>
+        <v>0.7204240003909768</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7453552303621422</v>
+        <v>0.7088603374967709</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7450768339256166</v>
+        <v>0.7088603374967709</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7478302532273042</v>
+        <v>0.712481760233469</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7475869399780773</v>
+        <v>0.7130034699192214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7453948516731713</v>
+        <v>0.7135602627922726</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7450813720493469</v>
+        <v>0.7111225921762747</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7267943043056322</v>
+        <v>0.7139393706669646</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7318099782868234</v>
+        <v>0.7138013069796343</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7337610224043678</v>
+        <v>0.7333094790932131</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7366875885806843</v>
+        <v>0.7337961055916666</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7348067108377376</v>
+        <v>0.7328205835328945</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7365121726441901</v>
+        <v>0.7328205835328945</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7274936989897438</v>
+        <v>0.7350828382123982</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7252642584356739</v>
+        <v>0.7350828382123982</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7230699010689027</v>
+        <v>0.7361262575839029</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7309419748518129</v>
+        <v>0.73532842052349</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7314987677248641</v>
+        <v>0.7350126718378005</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7314987677248641</v>
+        <v>0.7339669834044307</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7386737158855275</v>
+        <v>0.7514188618385684</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7454344729842004</v>
+        <v>0.7501321292178369</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7493014780319903</v>
+        <v>0.7523683769575022</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7513226885241323</v>
+        <v>0.7523898457736105</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7313912491011024</v>
+        <v>0.7425995419985897</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7339669834044307</v>
+        <v>0.735078300088668</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7274212635532811</v>
+        <v>0.7386295564507683</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.704953711137952</v>
+        <v>0.7410672270667663</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7022002918362644</v>
+        <v>0.7293326863597964</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6995872052837724</v>
+        <v>0.7377615530157577</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7114688859255329</v>
+        <v>0.744166940117712</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7114688859255329</v>
+        <v>0.7435399808700631</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7089610489349373</v>
+        <v>0.7444453365542376</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6981624089757106</v>
+        <v>0.7400215386333964</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6910621653133748</v>
+        <v>0.7369218255824508</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6897380804434794</v>
+        <v>0.7409268943175709</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6955844056105173</v>
+        <v>0.7257758446146434</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6932146323072519</v>
+        <v>0.738668130502475</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6920659633738506</v>
+        <v>0.738668130502475</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6851411356480092</v>
+        <v>0.7355729555752595</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6827362791574449</v>
+        <v>0.7204241749341972</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6852090329607418</v>
+        <v>0.7043031885555502</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6852090329607418</v>
+        <v>0.703746395682499</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.678487897173098</v>
+        <v>0.7197836013153578</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6656861992166501</v>
+        <v>0.7220334634262136</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6478688272790109</v>
+        <v>0.7125679845843428</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.658826999741676</v>
+        <v>0.700320810439081</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.658826999741676</v>
+        <v>0.6938735329642326</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6611220685466135</v>
+        <v>0.6995116280693425</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6635574701007463</v>
+        <v>0.6997900245058681</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6635574701007463</v>
+        <v>0.6981898122613122</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.662787909042037</v>
+        <v>0.7016448953089764</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6664512221516292</v>
+        <v>0.7327291228854089</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6518976338921043</v>
+        <v>0.7367228463112037</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6562093750654537</v>
+        <v>0.7363041171254826</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6587149429941842</v>
+        <v>0.7319108642682101</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6597889074292576</v>
+        <v>0.7319108642682101</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6762233734317291</v>
+        <v>0.7124739057885514</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6735446586283695</v>
+        <v>0.7236799296241736</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6646246273502244</v>
+        <v>0.7053464333838345</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6643111477264</v>
+        <v>0.7051710174473402</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6551127200117293</v>
+        <v>0.7284500212942728</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6579996648770168</v>
+        <v>0.7385209905676844</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6562987411942945</v>
+        <v>0.7377966362030566</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6521770775879523</v>
+        <v>0.7350126718378005</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6577053850074356</v>
+        <v>0.7352910682743261</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.656970907136025</v>
+        <v>0.7246983893151622</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6584499863856288</v>
+        <v>0.7100700965573095</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6566675510189833</v>
+        <v>0.7015506419699646</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6628296248717107</v>
+        <v>0.7013050596588728</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.638802528782177</v>
+        <v>0.6726686262052208</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5977152292450657</v>
+        <v>0.6764631958165481</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5919718845780592</v>
+        <v>0.6593055972519914</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5916934881415336</v>
+        <v>0.6549191515803143</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5917477710830756</v>
+        <v>0.6873433474596979</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5876351837241938</v>
+        <v>0.6872199454028807</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5711214750996642</v>
+        <v>0.7110953634338935</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5801207489998673</v>
+        <v>0.7349877121572843</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5103720563285881</v>
+        <v>0.7353713581557065</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4730646647722909</v>
+        <v>0.7521329181531931</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4691512312278767</v>
+        <v>0.735095230781046</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4601372956971606</v>
+        <v>0.7397668800748441</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4502440114221083</v>
+        <v>0.7375861370792636</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.471575287472684</v>
+        <v>0.7449433083620166</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.471575287472684</v>
+        <v>0.7438976199286467</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4807272866907304</v>
+        <v>0.7438976199286467</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.476586423330145</v>
+        <v>0.7367928381425808</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4727239564060853</v>
+        <v>0.6945579169313906</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4727239564060853</v>
+        <v>0.6801310470498705</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4973937206331032</v>
+        <v>0.6787786861782714</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4964532817616298</v>
+        <v>0.6738988068225454</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.495618092452053</v>
+        <v>0.6489890456674883</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4933535687106841</v>
+        <v>0.6489890456674883</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4961024498886414</v>
+        <v>0.6408181538912665</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4983296213808463</v>
+        <v>0.6360808763466009</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5</v>
+        <v>0.5839175876730596</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5</v>
+        <v>0.5797981931285825</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4994432071269488</v>
+        <v>0.5797981931285825</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4994432071269488</v>
+        <v>0.5788577542571092</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4991648106904232</v>
+        <v>0.5869754103511111</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4991648106904232</v>
+        <v>0.61363025462365</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4994432071269488</v>
+        <v>0.5741951812107714</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4994432071269488</v>
+        <v>0.5597332281419525</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4994432071269488</v>
+        <v>0.5574709734624488</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4994432071269488</v>
+        <v>0.5489674023081595</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4991648106904232</v>
+        <v>0.520724912902933</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4991648106904232</v>
+        <v>0.520724912902933</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.5199995112789829</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.5192887712855457</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.5242252026446789</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.5193407851652226</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.5169642046763619</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.5196078362924227</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.5208991070368845</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4997566867507732</v>
+        <v>0.5214558999099357</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4997566867507732</v>
+        <v>0.5237408452080904</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.5121534444359113</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.5043232610258952</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.5108656645558574</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.5108656645558574</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.49632429432176</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.499239515188751</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4982990763172777</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.499447745250679</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.4994828284379778</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.4992044320014522</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5003485628111233</v>
+        <v>0.4979154303188555</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5006620424349477</v>
+        <v>0.4976370338823299</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.4976370338823299</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.4973258233203706</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4973258233203706</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.5021728885506629</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.5021728885506629</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.4973982587568334</v>
       </c>
     </row>
   </sheetData>
